--- a/data/data of the formulation.xlsx
+++ b/data/data of the formulation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarw\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9A72D2-EC0C-48FE-9D16-E16518439286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CE9E83-AED3-47BC-8120-092FA33185DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4AE678F9-5763-43B8-B4E3-EEE05CCF35ED}"/>
   </bookViews>
@@ -558,7 +558,7 @@
         <v>120</v>
       </c>
       <c r="D6">
-        <v>176.8</v>
+        <v>125.6</v>
       </c>
       <c r="E6" s="1">
         <v>0.51988000000000001</v>
@@ -604,7 +604,7 @@
         <v>180</v>
       </c>
       <c r="D8">
-        <v>380.8</v>
+        <v>228.2</v>
       </c>
       <c r="E8" s="1">
         <v>0.79781999999999997</v>
@@ -627,7 +627,7 @@
         <v>120</v>
       </c>
       <c r="D9">
-        <v>228.2</v>
+        <v>200.2</v>
       </c>
       <c r="E9" s="1">
         <v>0.70350000000000001</v>
@@ -673,7 +673,7 @@
         <v>60</v>
       </c>
       <c r="D11">
-        <v>125.6</v>
+        <v>143.6</v>
       </c>
       <c r="E11" s="1">
         <v>0.45872000000000002</v>
